--- a/data/trans_dic/P3A$yo-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,82; 59,95</t>
+          <t>52,2; 60,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,68; 86,85</t>
+          <t>82,82; 86,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,08; 75,16</t>
+          <t>71,09; 75,27</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,89; 66,97</t>
+          <t>40,61; 67,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,31; 95,81</t>
+          <t>92,28; 95,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,27; 81,46</t>
+          <t>62,52; 81,8</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,93; 76,55</t>
+          <t>68,84; 76,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,66; 92,68</t>
+          <t>87,57; 92,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,25; 84,07</t>
+          <t>79,13; 83,86</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,22; 66,63</t>
+          <t>46,48; 66,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,16; 92,98</t>
+          <t>90,26; 92,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,04; 80,21</t>
+          <t>67,67; 80,08</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>266844; 308711</t>
+          <t>268785; 310912</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>624677; 656181</t>
+          <t>625679; 656571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>903045; 954901</t>
+          <t>903201; 956313</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>959061; 1533206</t>
+          <t>929677; 1536495</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2064642; 2142768</t>
+          <t>2063978; 2136282</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2863376; 3686542</t>
+          <t>2829615; 3702192</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>445741; 494959</t>
+          <t>445163; 492993</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>578951; 612086</t>
+          <t>578385; 612140</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1035817; 1098824</t>
+          <t>1034284; 1096074</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1664012; 2299139</t>
+          <t>1604062; 2294315</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3293300; 3396277</t>
+          <t>3296788; 3393953</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4762116; 5697745</t>
+          <t>4807089; 5688597</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$yo-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,2; 60,38</t>
+          <t>52,28; 60,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,82; 86,9</t>
+          <t>82,96; 86,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,09; 75,27</t>
+          <t>71,06; 75,3</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>79,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,61; 67,12</t>
+          <t>63,06; 67,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,28; 95,52</t>
+          <t>91,3; 94,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,52; 81,8</t>
+          <t>77,61; 80,43</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,84; 76,24</t>
+          <t>68,56; 75,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,57; 92,68</t>
+          <t>87,66; 92,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,13; 83,86</t>
+          <t>79,19; 83,89</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,48; 66,49</t>
+          <t>63,64; 67,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,26; 92,92</t>
+          <t>89,68; 91,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,67; 80,08</t>
+          <t>77,33; 79,47</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>288546</t>
+          <t>325784</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>641382</t>
+          <t>698660</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>929928</t>
+          <t>1024444</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>268785; 310912</t>
+          <t>302427; 348613</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>625679; 656571</t>
+          <t>681969; 714918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>903201; 956313</t>
+          <t>995278; 1054637</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1354415</t>
+          <t>1461796</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2101599</t>
+          <t>2017501</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3456014</t>
+          <t>3479297</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>929677; 1536495</t>
+          <t>1405871; 1509290</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2063978; 2136282</t>
+          <t>1981361; 2043463</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2829615; 3702192</t>
+          <t>3414702; 3538790</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>470459</t>
+          <t>514603</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>597713</t>
+          <t>663039</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1068172</t>
+          <t>1177642</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>445163; 492993</t>
+          <t>487830; 540067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>578385; 612140</t>
+          <t>644181; 677799</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1034284; 1096074</t>
+          <t>1145388; 1213431</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2113420</t>
+          <t>2302183</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3340694</t>
+          <t>3379200</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5454113</t>
+          <t>5681383</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1604062; 2294315</t>
+          <t>2239892; 2364467</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3296788; 3393953</t>
+          <t>3342360; 3417286</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4807089; 5688597</t>
+          <t>5603862; 5759016</t>
         </is>
       </c>
     </row>
